--- a/refunds.xlsx
+++ b/refunds.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Payments Reconciliation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Payments Reconciliation\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -5751,6 +5751,7 @@
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="7" max="7" width="46.42578125" customWidth="1"/>
     <col min="8" max="8" width="20.42578125" customWidth="1"/>
